--- a/Сверка_К4_расчет.xlsx
+++ b/Сверка_К4_расчет.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Открытые вопросы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Базовые материалы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - сталь итого" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - по позициям (К4)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пристройка К3-К4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пристройка К4-К5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПД этаж1 vs Модель" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Базовые материалы" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - сталь итого" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - по позициям (К4)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пристройка К3-К4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пристройка К4-К5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -128,6 +129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,17 +532,17 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>СВ-3.2 (внутр. СКЦ 80мм) — что за 2.6 м²?</t>
+          <t>СВ-3.2 (внутр. СКЦ 80мм) — РЕШЕНО</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>M=2.6 м², но сумма собственных этажных ячеек этой же строки в смете ≈11.1 м² — противоречие ВНУТРИ сметы, до сравнения с моделью. Модель по всему типу «111_СКЦ 80» даёт 155 м² (материал слоя которого к тому же почему-то указан как «Газобетон», а не «СКЦ»).</t>
+          <t>M=2.6 м2 в смете, оказывается, — это значение этажа 1 из ПД (там 2.59 м2, подтверждено моделью с точностью до 3-го знака: 2.594/32.419). Сама цифра верна, просто M заполнен не тем смыслом (этаж 1 вместо суммы по этажам/типового этажа).</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>К какому узлу/помещению относится эта строка? Без этого не могу понять, какое подмножество стен считать.</t>
+          <t>Только поправить смысл M в этой строке — расхождений с моделью нет.</t>
         </is>
       </c>
     </row>
@@ -550,17 +552,17 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>СВ-1.3 (облицовка ГКЛВ) — разрыв модель↔проект</t>
+          <t>СВ-1.3 (облицовка ГКЛВ) — частично прояснено</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Смета ожидает 7.9 м² на КАЖДОМ из 18 этажей. В модели нашёл только 1 тип с ГКЛВ, и он есть ТОЛЬКО на этаже 1 (Mark-параметр там вообще «ГВ-1.1» — марка с другого листа!). На этажах 2-18 — ни одного элемента.</t>
+          <t>Этаж 1 (65.9 м2, марка ГВ-1.1, тамбур) подтверждён ПД как верный — это НЕ ошибка. Но смета отдельно ожидает ~7.9 м2/этаж на КАЖДОМ из этажей 2-18 (видимо, обшивка шахты) — этого в модели по-прежнему нет ни на одном типовом этаже.</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Подтвердить: модели правда не хватает на типовых этажах (надо домоделировать), или решение изменилось и строку пора снимать?</t>
+          <t>Подтвердить: это реальный пробел в модели (домоделировать на типовых этажах) или строку пора снимать?</t>
         </is>
       </c>
     </row>
@@ -649,6 +651,266 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ПД: объём м3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ПД: площадь м2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Модель (искл. пристройка+ТП) м3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Модель м2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Совпадение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ГВ-1.1 (ГКЛВ, зашивка 87.5мм)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5.766</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>65.896</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>СВ-1.0 (внутр. 300мм — отдельная марка, не путать со сметной строкой 7)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>СВ-1.1 (внутр. 250мм)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.782</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>11.127</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>СВ-1.2 (внутр. 200мм)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>9.236000000000001</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46.181</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>точно (после искл. тега «ТП»; без него было бы 41.057/205.287)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>СВ-1.4 (100мм)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>СВ-3.1 (СКЦ 190мм)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>16.528</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>СВ-3.2 (СКЦ 80мм)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>32.419</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>СН-1.2 (наруж. 250мм)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Вывод: этаж 1 модели полностью и точно соответствует ПД по всем 8 маркам — проверено впрямую, не через смету.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Важно: на этаже 1 обнаружена третья категория тегов Comments=«ТП» (техническое помещение, 39 стен) в дополнение к «пристройка К3/К4»/«К4/К5» — все искл. только на эт.1, типовых этажей не касается.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1005,7 +1267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1259,7 +1521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2015,7 +2277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2155,7 +2417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Сверка_К4_расчет.xlsx
+++ b/Сверка_К4_расчет.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Открытые вопросы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПД этаж1 vs Модель" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПД этаж1 (4 корпуса)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Базовые материалы" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - сталь итого" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перемычки - по позициям (К4)" sheetId="5" state="visible" r:id="rId5"/>
@@ -45,7 +45,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2D9F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -130,6 +145,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -642,6 +666,26 @@
       <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Подтвердить: модель — источник истины (тогда смету поправить под неё), или наоборот - эти позиции надо перемоделировать под сметный типоразмер?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ЗАКРЫТО: этаж 1 всех 4 корпусов сверен с ПД напрямую</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>31 из 31 сравнений (К3×8, К4×8, К5×8, К6×7) — точное совпадение модели с ПД «Ведомость материалов кладочных стен 1 этажа» после исключения тегов соседних зон (своя система в каждом корпусе — см. лист «ПД этаж1 (4 корпуса)»).</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Ничего не требуется — раздел закрыт. К сведению: в К3 у пары типов Mark-параметр устарел (не влияет на числа).</t>
         </is>
       </c>
     </row>
@@ -656,256 +700,1074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Корпус</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Марка</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ПД: объём м3</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ПД: площадь м2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Модель (искл. пристройка+ТП) м3</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Модель (искл. посторонние зоны) м3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Модель м2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Совпадение</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Что исключено из наивного счёта</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>СВ-1.1 (250мм; Mark в модели ошибочно «СН-1.1»)</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>СВ-1.2 (200мм)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>134.59</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>26.918</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>134.591</v>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>СВ-1.3 (150мм)</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>4.865</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>32.435</v>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>СВ-1.4 (100мм)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>9.882999999999999</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>98.886</v>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>искл. «Кладка_ПОН» (10.510/105.104)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>СВ-2.2 (ПГП 80мм)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>СВ-3.2 (80мм; Mark в модели ошибочно «СВ-3.3»)</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>35.899</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>СН-1.1 (250мм)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>4.793</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>19.173</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>искл. пустые/иные теги</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>К3</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>СН-1.2 (300мм)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>16.224</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>искл. пустые теги (4.672/15.574)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>ГВ-1.1 (ГКЛВ, зашивка 87.5мм)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="C10" s="2" t="n">
         <v>5.77</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D10" s="2" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>5.766</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>65.896</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>СВ-1.0 (внутр. 300мм — отдельная марка, не путать со сметной строкой 7)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>СВ-1.0 (внутр. 300мм — отдельная марка)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>1.32</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D11" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E11" s="2" t="n">
         <v>1.32</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>СВ-1.1 (внутр. 250мм)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>2.78</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D12" s="2" t="n">
         <v>11.1</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E12" s="2" t="n">
         <v>2.782</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>11.127</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>СВ-1.2 (внутр. 200мм)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>9.24</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D13" s="2" t="n">
         <v>46.2</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>9.236000000000001</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>46.181</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>точно (после искл. тега «ТП»; без него было бы 41.057/205.287)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>искл. «ТП» (без него было бы 41.057/205.287)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>СВ-1.4 (100мм)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D14" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>19.15</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>СВ-3.1 (СКЦ 190мм)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>3.14</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>3.14</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>16.528</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>СВ-3.2 (СКЦ 80мм)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>2.59</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D16" s="2" t="n">
         <v>32.4</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>2.594</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>32.419</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>К4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>СН-1.2 (наруж. 250мм)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>1.03</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>точно</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Вывод: этаж 1 модели полностью и точно соответствует ПД по всем 8 маркам — проверено впрямую, не через смету.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Важно: на этаже 1 обнаружена третья категория тегов Comments=«ТП» (техническое помещение, 39 стен) в дополнение к «пристройка К3/К4»/«К4/К5» — все искл. только на эт.1, типовых этажей не касается.</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>искл. «пристройка К3/К4», «пристройка К4/К5»</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>СВ-1.0 (300мм)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>4.945</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>16.484</v>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>СВ-1.1 (250мм)</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>41.175</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>164.632</v>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>искл. 1 нетегированную стену</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>СВ-1.2 (200мм)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>22.886</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>114.431</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>СВ-1.4 (100мм)</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>35.311</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>353.648</v>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>искл. 2 нетегированные стены</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>СВ-3.1 (190мм)</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>3.116</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>16.403</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>искл. 1 нетегированную стену</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>СВ-3.2 (80мм)</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>27.786</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>СН-1.1 (300мм)</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>20.566</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>68.553</v>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>искл. 18 нетегированных стен</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>СН-1.2 (250мм)</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>18.347</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>73.634</v>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>искл. 4 нетегированные стены</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>СВ-1.2 (200мм)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>5.329</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>26.648</v>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>искл. «К5/К6» (30.980/155.060 — граница с К5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>СВ-1.3 (150мм)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>СВ-1.4 (100мм)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>30.845</v>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>искл. «К5/К6», «Кладка_ПОН», пустые</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>СВ-2.2 (ПГП 80мм)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>11.804</v>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>СВ-3.3 (80мм)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>29.163</v>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>СН-1.1 (300мм)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>7.759</v>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>искл. «К5/К6» (13.834/46.113)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>К6</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>СН-1.2 (250мм)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>2.677</v>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>точно</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>искл. «К5/К6» (22.288/89.165 — основная часть объёма!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО: 31 из 31 сравнений — точное совпадение (расхождение только в округлении, 3-й знак). Модели всех 4 корпусов на этаже 1 полностью соответствуют ПД.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>В каждом корпусе своя система тегов Comments для соседних/технических зон, которые надо исключать: К3='Кладка_ПОН'; К4='пристройка К3/К4'/'пристройка К4/К5'/'ТП'; К6='К5/К6' (граница с К5), 'Бизнес', 'Кладка_ПОН'. Без исключения расхождения доходили до 35х.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Побочно: у части типов в К3 Mark-параметр внутри модели устарел/неверен (см. пометки в колонке 'Марка') — сами количества это не затрагивает, сверка шла по материалу+толщине слоя, а не по Mark.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
